--- a/塗料メーカー_製造フローINOUT.xlsx
+++ b/塗料メーカー_製造フローINOUT.xlsx
@@ -15,7 +15,8 @@
     <sheet name="③-3 粉体塗料" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="③-4 電着塗料" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="③-5 UV硬化塗料" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="出典_参考文献" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="用語集" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="典拠" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,12 +62,23 @@
     </font>
     <font>
       <name val="Yu Gothic"/>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
       <color rgb="000563C1"/>
       <sz val="9"/>
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -106,6 +118,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F4B084"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6E0B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE4E1"/>
       </patternFill>
     </fill>
   </fills>
@@ -193,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -251,8 +288,35 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -622,7 +686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E20"/>
+  <dimension ref="B2:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -795,83 +859,1113 @@
     <row r="14">
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>出典</t>
+          <t>用語集</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>参考文献</t>
+          <t>専門用語の解説</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>JPMA・環境省・経産省・装置メーカー資料 等</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="3" t="inlineStr">
+          <t>原材料・製造プロセス・製品・品質・物流・規制・環境 のカテゴリ別 60+ 用語</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>典拠</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>記述の根拠</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Excel 各記述に対する 法令 / 公的資料 / 業界資料 / 装置メーカー 等の典拠マッピング</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>テンプレート凡例 (リン酸 PDF と同形式)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="9" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>上段 (IN)</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>工程に投入される原料・ユーティリティ</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="10" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>中段 (工程)</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>工程名・装置・概要</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="11" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>下段 (OUT)</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>工程から出る中間品・廃棄物・排出</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B18:E18"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="C19:E19"/>
+    <mergeCell ref="D15:E15"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="D13:E13"/>
-    <mergeCell ref="C18:E18"/>
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B2:E2"/>
+    <mergeCell ref="C21:E21"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="D12:E12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:G38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>典拠 (Excel 各シートの記述に対する根拠)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="B3" s="27" t="inlineStr">
+        <is>
+          <t>本シートは「主張 (記述内容) → 典拠 (根拠の情報源)」のマッピング。区分は 法令 / 公的資料 / 業界資料 / 装置メーカー / 学術 / 業者事例 / 推計 等。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>引用箇所</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>主張・記述内容</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>典拠区分</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>出典名</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="50" customHeight="1">
+      <c r="B6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>①製品タイプ一覧</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>塗料は溶剤系・水性・粉体・電着・UV 硬化に大別される</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>業界資料</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>JPMA (日本塗料工業会) 製品分類解説、モノタロウ「塗料の変遷 ─ 粉体塗料」</t>
+        </is>
+      </c>
+      <c r="G6" s="29" t="inlineStr">
+        <is>
+          <t>https://www.monotaro.com/note/readingseries/tosouqa/0416/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="50" customHeight="1">
+      <c r="B7" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>①製品タイプ一覧</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>溶剤系塗料は消防法第 4 類引火性液体に該当</t>
+        </is>
+      </c>
+      <c r="E7" s="30" t="inlineStr">
+        <is>
+          <t>法令</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>消防法 / 危険物の規制に関する政令 (e-Gov)</t>
+        </is>
+      </c>
+      <c r="G7" s="29" t="inlineStr">
+        <is>
+          <t>https://laws.e-gov.go.jp/law/334CO0000000306</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="50" customHeight="1">
+      <c r="B8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>①製品タイプ一覧</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>水性塗料は VOC 削減型として推奨されるが冬季の凍結対策と防腐剤添加が必要</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>業界資料</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>JPMA「低 VOC 塗料」自主表示制度、関東塗料工業組合 解説</t>
+        </is>
+      </c>
+      <c r="G8" s="29" t="inlineStr">
+        <is>
+          <t>https://kantoko.com/blog/2024/04/90578/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="50" customHeight="1">
+      <c r="B9" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>①製品タイプ一覧</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>粉体塗料は VOC ゼロで塗着効率ほぼ 100% (理論値)</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>業界資料</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>NCC「塗着効率とは」、NCC「粉なのに塗料？」、ヒバラコーポレーション 粉体塗装解説</t>
+        </is>
+      </c>
+      <c r="G9" s="29" t="inlineStr">
+        <is>
+          <t>https://ncc-nice.com/ncc-coating/knowledge/basics/coatingefficiency/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="50" customHeight="1">
+      <c r="B10" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>①製品タイプ一覧</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>電着塗料はカチオン (自動車車体下塗) / アニオン (電子部品) の 2 系統</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>業界資料</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>関西ペイント技術資料、自動車塗装業界一般解説</t>
+        </is>
+      </c>
+      <c r="G10" s="29" t="inlineStr">
+        <is>
+          <t>https://asset.kansai.co.jp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="50" customHeight="1">
+      <c r="B11" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" s="28" t="inlineStr">
+        <is>
+          <t>②製造フロー比較</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>液体塗料の標準フローは 前練 → 分散 → 調合 → 調色 → ろ過 → 検査 → 充填</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>業界資料</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>Mixing Tank「塗料製造の方法」、JCT Machinery Paint Manufacturing Process、SR 塗装ブログ「塗料をつくる」</t>
+        </is>
+      </c>
+      <c r="G11" s="29" t="inlineStr">
+        <is>
+          <t>https://www.mixing-tank.com/ja/blog/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="50" customHeight="1">
+      <c r="B12" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>②製造フロー比較</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>ミルベース工程は顔料分散、レットダウン工程は樹脂・溶剤追加と定義される</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>業界資料</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>色材協会誌 庫本「塗料における分散」J-Stage、Yahoo 知恵袋 業界回答</t>
+        </is>
+      </c>
+      <c r="G12" s="29" t="inlineStr">
+        <is>
+          <t>https://www.jstage.jst.go.jp/article/shikizai1937/78/4/78_191/_pdf/-char/ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="50" customHeight="1">
+      <c r="B13" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" s="28" t="inlineStr">
+        <is>
+          <t>②製造フロー比較</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>粉体塗料は 配合 → 押出混練 → 冷却 → 粉砕 → 分級 のフロー</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>業界資料</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>ヒバラコーポレーション、日鉄防食、NCC、モノタロウ技術解説</t>
+        </is>
+      </c>
+      <c r="G13" s="29" t="inlineStr">
+        <is>
+          <t>https://kougyoutosou.com/technology/powder/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="50" customHeight="1">
+      <c r="B14" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>③-1 溶剤系液体塗料</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>樹脂・顔料・溶剤・添加剤の代表的配合比 (樹脂 35〜45%、顔料 15〜25%、溶剤 15〜25%、添加剤 5〜15%)</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>業界資料</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>サンノプコ「顔料分散と分散剤」、関西ペイント R&amp;D、業界教科書一般</t>
+        </is>
+      </c>
+      <c r="G14" s="29" t="inlineStr">
+        <is>
+          <t>https://www.sannopco.co.jp/feature/pigment-dispersion/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="50" customHeight="1">
+      <c r="B15" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" s="28" t="inlineStr">
+        <is>
+          <t>③-1 溶剤系液体塗料</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>ディスパー回転数 1,500〜3,000 rpm、ビーズ径 0.3〜2 mm</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>装置メーカー</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>アシザワ・ファインテック「ビーズミルで分散する」、淺田鉄工 製品情報</t>
+        </is>
+      </c>
+      <c r="G15" s="29" t="inlineStr">
+        <is>
+          <t>https://ashizawa.com/guidance/05.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="50" customHeight="1">
+      <c r="B16" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C16" s="28" t="inlineStr">
+        <is>
+          <t>③-1 溶剤系液体塗料</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>分散・練肉工程は塗料製造で最大の電力消費工程</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="inlineStr">
+        <is>
+          <t>学術/装置メーカー</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>関西ペイント R&amp;D「高度顔料分散システム」、色材協会誌 J-Stage</t>
+        </is>
+      </c>
+      <c r="G16" s="29" t="inlineStr">
+        <is>
+          <t>https://asset.kansai.co.jp/uploads/rd/paint_study/pdf/143/04.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="50" customHeight="1">
+      <c r="B17" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="C17" s="28" t="inlineStr">
+        <is>
+          <t>③-1 溶剤系液体塗料</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>充填容器は 1L / 4L / 14L / 16L / 20L (一斗缶) / 200L ドラム / IBC が一般的</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>業界資料</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>業界一般 (一斗缶 = 18L の規格、外壁塗装大百科 解説)</t>
+        </is>
+      </c>
+      <c r="G17" s="29" t="inlineStr">
+        <is>
+          <t>https://exterior-paint.net/%E4%B8%80%E6%96%97%E7%BC%B6%E3%81%A8%E3%81%AF%EF%BC%9F/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="50" customHeight="1">
+      <c r="B18" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="C18" s="28" t="inlineStr">
+        <is>
+          <t>③-1 溶剤系液体塗料</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>廃シンナー (引火点 70℃未満の廃油) は特別管理産業廃棄物に該当</t>
+        </is>
+      </c>
+      <c r="E18" s="30" t="inlineStr">
+        <is>
+          <t>法令</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>廃棄物処理法、e-reverse.com「廃塗料の廃棄注意点」、丸商「シンナーの廃棄物処理」</t>
+        </is>
+      </c>
+      <c r="G18" s="29" t="inlineStr">
+        <is>
+          <t>https://www.e-reverse.com/blog/law067/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="50" customHeight="1">
+      <c r="B19" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C19" s="28" t="inlineStr">
+        <is>
+          <t>③-1 溶剤系液体塗料</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>廃シンナーの蒸留再生 (社内設置) で処理コストを 1/3 程度に削減可能</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>業者事例</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>株式会社ネクストリー「溶剤回収装置で実際にシンナーを再生してみました」</t>
+        </is>
+      </c>
+      <c r="G19" s="29" t="inlineStr">
+        <is>
+          <t>https://nextry.jp/340/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="50" customHeight="1">
+      <c r="B20" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="C20" s="28" t="inlineStr">
+        <is>
+          <t>③-1 溶剤系液体塗料</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>釜内残・配管残のロス削減にピギング (配管内残液回収) が有効</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>業界資料/特許</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>コスモエンジニアリング パイプライニング、特許 JPH0940092A「配管内残液回収方法」</t>
+        </is>
+      </c>
+      <c r="G20" s="29" t="inlineStr">
+        <is>
+          <t>https://patents.google.com/patent/JPH0940092A/ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="50" customHeight="1">
+      <c r="B21" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="C21" s="28" t="inlineStr">
+        <is>
+          <t>③-2 水性液体塗料</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>水性塗料には防腐剤 (イソチアゾリン系等) の添加が必須</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>業界資料</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>三洋化成マガジン「水系塗料用分散剤・調色改良剤」、Lonza・Troy 製品資料</t>
+        </is>
+      </c>
+      <c r="G21" s="29" t="inlineStr">
+        <is>
+          <t>https://www.sanyo-chemical.co.jp/magazine/archives/1242</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="50" customHeight="1">
+      <c r="B22" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="C22" s="28" t="inlineStr">
+        <is>
+          <t>③-2 水性液体塗料</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>水性塗料の保管 pH は 8〜9 に維持 (アンモニア・AMP で調整)</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>業界資料</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>色材協会誌 解説テーマ「やさしい塗料物性」J-Stage</t>
+        </is>
+      </c>
+      <c r="G22" s="29" t="inlineStr">
+        <is>
+          <t>https://www.jstage.jst.go.jp/article/shikizai1937/67/6/67_393/_pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="50" customHeight="1">
+      <c r="B23" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="C23" s="28" t="inlineStr">
+        <is>
+          <t>③-2 水性液体塗料</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>VOC の主要発生源は塗料製造ではなく塗装時 (顧客側) である</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>公的資料</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>環境省 VOC 排出インベントリ、JPMA「塗料からの VOC 排出実態推計のまとめ」、関東塗料工業組合 解説</t>
+        </is>
+      </c>
+      <c r="G23" s="29" t="inlineStr">
+        <is>
+          <t>https://www.toryo.or.jp/jp/book/voch2022.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="50" customHeight="1">
+      <c r="B24" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="C24" s="28" t="inlineStr">
+        <is>
+          <t>③-3 粉体塗料</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>押出混練は二軸エクストルーダーで樹脂を 90〜120℃に加熱しながら混練</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>業界資料</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>ヒバラコーポレーション 粉体塗装解説、日鉄防食 粉体塗装ページ、ドナウ商事 押出機解説</t>
+        </is>
+      </c>
+      <c r="G24" s="29" t="inlineStr">
+        <is>
+          <t>https://www.donau.co.jp/cate-industrial/aboutextruder/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="50" customHeight="1">
+      <c r="B25" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="C25" s="28" t="inlineStr">
+        <is>
+          <t>③-3 粉体塗料</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>粉体塗料の平均粒径は 20〜40 μm に分級</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>業界資料</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>NCC「粉なのに塗料？」、モノタロウ 粉体塗料解説</t>
+        </is>
+      </c>
+      <c r="G25" s="29" t="inlineStr">
+        <is>
+          <t>https://ncc-3clab.com/resolution/painting/2461/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="50" customHeight="1">
+      <c r="B26" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="C26" s="28" t="inlineStr">
+        <is>
+          <t>③-3 粉体塗料</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>オーバースプレー粉は回収用ブースで再利用可能、理論塗着効率はほぼ 100%</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>業界資料</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>NCC「塗着効率とは」、ヒバラコーポレーション</t>
+        </is>
+      </c>
+      <c r="G26" s="29" t="inlineStr">
+        <is>
+          <t>https://ncc-nice.com/ncc-coating/knowledge/basics/coatingefficiency/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="50" customHeight="1">
+      <c r="B27" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="C27" s="28" t="inlineStr">
+        <is>
+          <t>③-4 電着塗料</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>電着塗料はタンクローリーで自動車 OEM 塗装ラインに直送する VMI 運用が標準</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>業界一般</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>自動車塗装業界一般解説、塗料商業誌、関西ペイント技術資料</t>
+        </is>
+      </c>
+      <c r="G27" s="29" t="inlineStr">
+        <is>
+          <t>https://asset.kansai.co.jp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="50" customHeight="1">
+      <c r="B28" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="C28" s="28" t="inlineStr">
+        <is>
+          <t>③-4 電着塗料</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>電着塗料の固形分は 15〜25%、洗浄水中の塗料分は UF (限外ろ過) で回収・再利用</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>業界教科書</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>電着塗装業界教科書、自動車塗装ライン技術資料</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>(専門書: 電着塗装の理論と実際 等)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="50" customHeight="1">
+      <c r="B29" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="C29" s="28" t="inlineStr">
+        <is>
+          <t>③-5 UV硬化塗料</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>UV 硬化塗料は光開始剤 (Irgacure 等) を含有し UV 照射で瞬時に硬化</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>メーカー</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>BASF Irgacure シリーズ製品データ、業界一般</t>
+        </is>
+      </c>
+      <c r="G29" s="29" t="inlineStr">
+        <is>
+          <t>https://www.basf.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="50" customHeight="1">
+      <c r="B30" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="C30" s="28" t="inlineStr">
+        <is>
+          <t>③-5 UV硬化塗料</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>感光性のため遮光下 (黄色灯) で製造・遮光容器で保管が必要</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>業界一般</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>業界教科書、装置メーカー安全資料</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>(専門書: UV 硬化技術ハンドブック)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="50" customHeight="1">
+      <c r="B31" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="C31" s="28" t="inlineStr">
+        <is>
+          <t>全シート共通</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>10t バッチサイズ・歩留まり ≒ 97.5% は業界一般値の概算 (確定統計なし)</t>
+        </is>
+      </c>
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>推計</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>化学・配合系製造業は装置内残留や微飛沫で 100% 歩留まりが成立しない (歩留まり業界解説)</t>
+        </is>
+      </c>
+      <c r="G31" s="29" t="inlineStr">
+        <is>
+          <t>https://www.smartmat.io/column/production_management/8198</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="50" customHeight="1">
+      <c r="B32" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="C32" s="28" t="inlineStr">
+        <is>
+          <t>全シート共通</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>塗料は消防法 第 4 類 (第 1〜3 石油類) として倍数管理される</t>
+        </is>
+      </c>
+      <c r="E32" s="30" t="inlineStr">
+        <is>
+          <t>法令</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
+        <is>
+          <t>消防法、危険物の規制に関する政令、三協化学 解説、化研テック 解説</t>
+        </is>
+      </c>
+      <c r="G32" s="29" t="inlineStr">
+        <is>
+          <t>https://www.sankyo-chem.com/news/post-689/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="50" customHeight="1">
+      <c r="B33" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="C33" s="28" t="inlineStr">
+        <is>
+          <t>全シート共通</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>原材料費は塗料原価の 60〜70%、TiO₂・樹脂が中核</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>業界資料</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="inlineStr">
+        <is>
+          <t>JPMA コーティング・ケア環境管理指標、業界 IR 一般</t>
+        </is>
+      </c>
+      <c r="G33" s="29" t="inlineStr">
+        <is>
+          <t>https://www.toryo.or.jp/jp/anzen/cc/03_feature.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="50" customHeight="1">
+      <c r="B34" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="C34" s="28" t="inlineStr">
+        <is>
+          <t>全シート共通</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>排ガス VOC 処理は RTO (蓄熱燃焼) / 活性炭吸着 / 触媒燃焼 / 冷却凝縮 の組合せ</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>業界資料</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr">
+        <is>
+          <t>経産省 VOC 排出削減のための取組事例、KLV「VOC 規制の基本」</t>
+        </is>
+      </c>
+      <c r="G34" s="29" t="inlineStr">
+        <is>
+          <t>https://www.meti.go.jp/policy/voc/r1_jirei_2.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="50" customHeight="1">
+      <c r="B35" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="C35" s="28" t="inlineStr">
+        <is>
+          <t>全シート共通</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>PRTR で塗料関連物質の排出量が報告されている</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
+        <is>
+          <t>公的資料</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="inlineStr">
+        <is>
+          <t>経産省 PRTR 制度 塗料に係る排出量</t>
+        </is>
+      </c>
+      <c r="G35" s="29" t="inlineStr">
+        <is>
+          <t>https://www.meti.go.jp/policy/chemical_management/law/prtr/r4kohyo/05todokedegaiyou/syousai/5.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="45" customHeight="1">
+      <c r="B38" s="31" t="inlineStr">
+        <is>
+          <t>注: 工程別の電力 (kWh/t)・歩留まり (%)・廃棄物単価などの定量値は業界一般値の概算であり、工場・製品種・年度で大きく変動します。実プロジェクト適用時は対象工場の実測値および JPMA コーティング・ケア環境管理指標等の公表値で校正してください。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B38:G38"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId28"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -9154,25 +10248,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:D32"/>
+  <dimension ref="B2:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>出典・参考文献 (Web 整合確認に使用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>用語集 (塗料製造で頻出する専門用語)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
       <c r="B4" s="6" t="inlineStr">
         <is>
           <t>No.</t>
@@ -9180,429 +10276,2135 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>情報源</t>
+          <t>カテゴリ</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="7" t="n">
+          <t>用語</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>読み</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>英語表記</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>解説</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="B5" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>日本塗料工業会 (JPMA) VOC規制関連情報</t>
-        </is>
-      </c>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t>https://www.toryo.or.jp/jp/anzen/VOC/index.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="7" t="n">
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>原材料</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>樹脂 (バインダー)</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>じゅし／-</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>Resin / Binder</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>塗膜の骨格を形成する高分子成分。アクリル・エポキシ・ポリウレタン・アルキッド・フッ素・シリコーン等。塗料原価の最大費目。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="B6" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>JPMA 塗料からのVOC排出実態推計のまとめ 2022年度</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>https://www.toryo.or.jp/jp/book/voch2022.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="7" t="n">
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>原材料</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>顔料</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>がんりょう</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>Pigment</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>塗料に着色と隠蔽性を与える微粒子。無機顔料 (TiO₂・酸化鉄等) と有機顔料 (アゾ・フタロシアニン等) に大別。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="B7" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>JPMA コーティング・ケア環境管理指標</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>https://www.toryo.or.jp/jp/anzen/cc/03_feature.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="7" t="n">
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>原材料</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>酸化チタン (TiO₂)</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>さんかちたん</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>Titanium Dioxide</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>白色顔料の代表。塗料用顔料の 6 割超を占め、価格変動が塗料原価を大きく左右する。製法は塩素法と硫酸法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="B8" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>関東塗料工業組合 2022年度塗料VOC排出推計</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>https://kantoko.com/blog/2024/04/90578/</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="7" t="n">
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>原材料</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>体質顔料</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>たいしつがんりょう</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>Extender Pigment</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>炭酸カルシウム・タルク・硫酸バリウム等の増量・物性調整用顔料。安価で耐久性・粘性向上に寄与。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="38" customHeight="1">
+      <c r="B9" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>庫本「塗料における分散」色材協会誌 (J-Stage)</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>https://www.jstage.jst.go.jp/article/shikizai1937/78/4/78_191/_pdf/-char/ja</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="7" t="n">
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>原材料</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>溶剤</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>ようざい</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>Solvent</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>樹脂を溶解・希釈し塗料に流動性を与える液体。トルエン・キシレン・MEK 等の有機溶剤と水。消防法第 4 類対象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="38" customHeight="1">
+      <c r="B10" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>塗料における最近の顔料分散とそのプロセス (J-Stage)</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>https://www.jstage.jst.go.jp/article/shikizai/87/6/87_204/_pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="7" t="n">
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>原材料</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>添加剤</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>てんかざい</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>Additive</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>数 % の配合だが品質を決定する補助材。分散剤・消泡剤・レベリング剤・UV 吸収剤・防腐剤 等。BYK・Evonik 等が寡占。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="38" customHeight="1">
+      <c r="B11" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Mixing Tank 塗料製造の方法</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t>https://www.mixing-tank.com/ja/blog/</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="7" t="n">
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>原材料</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>分散剤</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>ぶんさんざい</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>Dispersant</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>顔料を樹脂・溶剤中に均一分散させる界面活性剤系添加剤。塗料の色再現性・貯蔵安定性を担保。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="38" customHeight="1">
+      <c r="B12" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>JCT Machinery Paint Manufacturing Process</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t>https://www.mixmachinery.com/news/paint-manufacturing-process-jct-machinery.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="7" t="n">
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>原材料</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>消泡剤</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>しょうほうざい</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>Defoamer / Antifoam</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>気泡を破壊・抑制する添加剤。シリコーン系・鉱油系・アクリル系がある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="38" customHeight="1">
+      <c r="B13" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>アシザワ・ファインテック ビーズミルガイド</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>https://ashizawa.com/guidance/05.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="7" t="n">
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>原材料</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>レベリング剤</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>Leveling Agent</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>塗膜表面の平滑性を向上させる添加剤。シリコーン系・アクリル系。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="38" customHeight="1">
+      <c r="B14" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>関西ペイント R&amp;D 高度顔料分散システム</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t>https://asset.kansai.co.jp/uploads/rd/paint_study/pdf/143/04.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="7" t="n">
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>原材料</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>HALS / UV吸収剤</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>Hindered Amine Light Stabilizer</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>紫外線によるラジカル劣化を捕捉するアミン系添加剤。屋外用途の耐候性向上に必須。BASF Tinuvin が代表。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="38" customHeight="1">
+      <c r="B15" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>サンノプコ 顔料分散解説</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="inlineStr">
-        <is>
-          <t>https://www.sannopco.co.jp/feature/pigment-dispersion/</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="B16" s="7" t="n">
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>原材料</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>硬化剤</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>こうかざい</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>Curing Agent / Crosslinker</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>樹脂と反応して三次元架橋を起こさせる薬剤。イソシアネート・アミン・ジシアンジアミド・TGIC 等。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="38" customHeight="1">
+      <c r="B16" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>ヒバラコーポレーション 粉体塗装</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>https://kougyoutosou.com/technology/powder/</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="7" t="n">
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>原材料</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>ブロックイソシアネート</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>Blocked Isocyanate</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>イソシアネート基をブロック剤で保護し、加熱で再活性化させる硬化剤。電着塗料・粉体塗料で使用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="38" customHeight="1">
+      <c r="B17" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>日鉄防食 粉体塗装</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t>https://acc.nipponsteel.com/powder-coating/</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="B18" s="7" t="n">
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>原材料</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>光開始剤</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>ひかりかいしざい</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>Photoinitiator</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>UV 照射でラジカルを発生し UV 塗料を瞬時に硬化させる。Irgacure (BASF, 旧 Ciba) が代表。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="38" customHeight="1">
+      <c r="B18" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>NCC 粉なのに塗料？</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t>https://ncc-3clab.com/resolution/painting/2461/</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="B19" s="7" t="n">
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>原材料</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>TGIC</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>Triglycidyl Isocyanurate</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>ポリエステル粉体塗料の代表的な硬化剤。耐候性に優れる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="38" customHeight="1">
+      <c r="B19" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>NCC 塗着効率とは</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>https://ncc-nice.com/ncc-coating/knowledge/basics/coatingefficiency/</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="B20" s="7" t="n">
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>原材料</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>防腐剤</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>ぼうふざい</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>Biocide / Preservative</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>水性塗料に必須。イソチアゾリン系等が代表。容器内での細菌・カビ繁殖を防止。Lonza・Troy 等。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="38" customHeight="1">
+      <c r="B20" s="22" t="n">
         <v>16</v>
       </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>モノタロウ 粉体塗料解説</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr">
-        <is>
-          <t>https://www.monotaro.com/note/readingseries/tosouqa/0416/</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="7" t="n">
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>製造プロセス</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>ミルベース</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>Mill Base</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>顔料を樹脂・溶剤中に高濃度で微分散させた中間製品。塗料製造の根幹工程の産物。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="38" customHeight="1">
+      <c r="B21" s="22" t="n">
         <v>17</v>
       </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>e-Gov 危険物の規制に関する政令</t>
-        </is>
-      </c>
-      <c r="D21" s="21" t="inlineStr">
-        <is>
-          <t>https://laws.e-gov.go.jp/law/334CO0000000306</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="7" t="n">
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>製造プロセス</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>レットダウン</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>Let-down / Thinning</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>ミルベースに残りの樹脂・溶剤・添加剤を加えて最終塗料に調合する工程。「調合工程」とも呼ぶ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="38" customHeight="1">
+      <c r="B22" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>三協化学 消防法と有機溶剤・指定数量</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr">
-        <is>
-          <t>https://www.sankyo-chem.com/news/post-689/</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="B23" s="7" t="n">
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>製造プロセス</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>前練</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>まえねり</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>Pre-mixing</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>本格的な分散の前に行う粗混合。ディスパーザー等の高速撹拌で実施。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="38" customHeight="1">
+      <c r="B23" s="22" t="n">
         <v>19</v>
       </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>化研テック 指定数量とは</t>
-        </is>
-      </c>
-      <c r="D23" s="21" t="inlineStr">
-        <is>
-          <t>https://www.kaken-tech.co.jp/trouble/%E6%8C%87%E5%AE%9A%E6%95%B0%E9%87%8F/</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="7" t="n">
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>製造プロセス</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>分散・練肉</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>ぶんさん・れんにく</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>Dispersion / Milling</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>顔料凝集体を nm 単位まで微粒化する工程。ビーズミル・サンドミル・三本ロール等を使用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="38" customHeight="1">
+      <c r="B24" s="22" t="n">
         <v>20</v>
       </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>e-reverse.com 廃塗料の廃棄解説</t>
-        </is>
-      </c>
-      <c r="D24" s="21" t="inlineStr">
-        <is>
-          <t>https://www.e-reverse.com/blog/law067/</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="B25" s="7" t="n">
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>製造プロセス</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>ディスパーザー</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>Disperser / High-speed Mixer</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>高速回転羽根 (1,500〜3,000 rpm) で粗分散を行う装置。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="38" customHeight="1">
+      <c r="B25" s="22" t="n">
         <v>21</v>
       </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>丸商 シンナーの廃棄物処理</t>
-        </is>
-      </c>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t>https://marusho-eco.jp/column/how_to_dispose_of_thinner_waste/</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="B26" s="7" t="n">
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>製造プロセス</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>ビーズミル</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>Bead Mill</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>0.3〜2 mm の媒体ビーズと共に高速循環し顔料を微粒化する装置。塗料製造の主力分散機。アシザワ・淺田鉄工 等。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="38" customHeight="1">
+      <c r="B26" s="22" t="n">
         <v>22</v>
       </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>ネクストリー 溶剤回収装置事例</t>
-        </is>
-      </c>
-      <c r="D26" s="21" t="inlineStr">
-        <is>
-          <t>https://nextry.jp/340/</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="B27" s="7" t="n">
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>製造プロセス</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>サンドミル</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>Sand Mill</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>砂状メディアを使用する初期型分散機。ビーズミルの祖先にあたる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="38" customHeight="1">
+      <c r="B27" s="22" t="n">
         <v>23</v>
       </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>コスモエンジニアリング パイプライニング</t>
-        </is>
-      </c>
-      <c r="D27" s="21" t="inlineStr">
-        <is>
-          <t>https://www.cosmoeng.co.jp/service/ctg05/piping/pipelining.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="7" t="n">
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>製造プロセス</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>三本ロール</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>さんぼん-</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>Three-roll Mill</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>3 本の回転ロール間で高粘度ペーストを擦り合わせて分散させる装置。高粘度系で使用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="38" customHeight="1">
+      <c r="B28" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>環境省 廃棄物処理に関する統計</t>
-        </is>
-      </c>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t>https://www.env.go.jp/recycle/waste/wastetoukei_index.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="B29" s="7" t="n">
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>製造プロセス</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>調色</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>ちょうしょく</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>Tinting / Color Matching</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>目標色に合わせて着色剤を微量添加する工程。CCM や職人の目視で実施。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="38" customHeight="1">
+      <c r="B29" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>経産省 PRTR 塗料に係る排出量</t>
-        </is>
-      </c>
-      <c r="D29" s="21" t="inlineStr">
-        <is>
-          <t>https://www.meti.go.jp/policy/chemical_management/law/prtr/r4kohyo/05todokedegaiyou/syousai/5.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="40" customHeight="1">
-      <c r="B32" s="22" t="inlineStr">
-        <is>
-          <t>注: 工程別の電力 (kWh/t)・歩留まり・廃棄物単価などの定量値は業界一般値の概算であり、工場・製品種・年度で大きく変動。実プロジェクト適用時は対象工場の実測値および JPMA 公表値で上書き校正のこと。</t>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>製造プロセス</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>CCM</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>Computer Color Matching</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>分光測色計とコンピュータで自動的に色配合を提案する技術。再調色回数を削減。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="38" customHeight="1">
+      <c r="B30" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>製造プロセス</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>ろ過</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>ろか</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>Filtration</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>凝集物・異物を除去する工程。バッグフィルタ・カートリッジ式で目開き 50〜200 μm。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="38" customHeight="1">
+      <c r="B31" s="22" t="n">
+        <v>27</v>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>製造プロセス</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>押出混練</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>おしだしこんれん</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
+          <t>Extrusion / Melt Compounding</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>粉体塗料製造の中核工程。二軸エクストルーダーで樹脂を溶融させ顔料を分散。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="38" customHeight="1">
+      <c r="B32" s="22" t="n">
+        <v>28</v>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>製造プロセス</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>エクストルーダー</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
+        <is>
+          <t>Extruder</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>原料を加熱・混練しながら押し出す装置。粉体塗料製造で必須。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="38" customHeight="1">
+      <c r="B33" s="22" t="n">
+        <v>29</v>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>製造プロセス</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>分級</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>ぶんきゅう</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t>Classification / Sieving</t>
+        </is>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>粉砕粉を粒径別に分けて規格内のものを製品とする工程。気流分級機・篩を使用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="38" customHeight="1">
+      <c r="B34" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>製造プロセス</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>バッチ生産</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t>Batch Production</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>一定量を釜単位で生産する方式。塗料製造の標準形態。1 バッチ 数百 kg〜数十 t。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="38" customHeight="1">
+      <c r="B35" s="23" t="n">
+        <v>31</v>
+      </c>
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>製品</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>溶剤系塗料</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>ようざいけい-</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
+        <is>
+          <t>Solvent-borne Paint</t>
+        </is>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>有機溶剤を媒体とする塗料。乾燥が早く塗膜性能高いが VOC 排出大。消防法対象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="38" customHeight="1">
+      <c r="B36" s="23" t="n">
+        <v>32</v>
+      </c>
+      <c r="C36" s="23" t="inlineStr">
+        <is>
+          <t>製品</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>水性塗料</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>すいせい-</t>
+        </is>
+      </c>
+      <c r="F36" s="21" t="inlineStr">
+        <is>
+          <t>Water-borne Paint</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>水を媒体とする塗料。VOC 削減型。凍結 NG・防腐剤必要。建築用が中心。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="38" customHeight="1">
+      <c r="B37" s="23" t="n">
+        <v>33</v>
+      </c>
+      <c r="C37" s="23" t="inlineStr">
+        <is>
+          <t>製品</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>粉体塗料</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>ふんたい-</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="inlineStr">
+        <is>
+          <t>Powder Coating</t>
+        </is>
+      </c>
+      <c r="G37" s="13" t="inlineStr">
+        <is>
+          <t>溶剤を全く含まない粉末塗料。回収再利用可能、塗着効率ほぼ 100%。家電・自動車部品・建材で増勢。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="38" customHeight="1">
+      <c r="B38" s="23" t="n">
+        <v>34</v>
+      </c>
+      <c r="C38" s="23" t="inlineStr">
+        <is>
+          <t>製品</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>電着塗料</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>でんちゃく-</t>
+        </is>
+      </c>
+      <c r="F38" s="21" t="inlineStr">
+        <is>
+          <t>Electrodeposition (E-coat)</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>塗料を水中に分散し、電気泳動により素材表面に均一に析出させる塗料。自動車車体下塗の世界標準。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="38" customHeight="1">
+      <c r="B39" s="23" t="n">
+        <v>35</v>
+      </c>
+      <c r="C39" s="23" t="inlineStr">
+        <is>
+          <t>製品</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>カチオン電着塗料</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F39" s="21" t="inlineStr">
+        <is>
+          <t>Cationic E-coat</t>
+        </is>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>アミン中和エポキシ樹脂を使用。自動車車体下塗で防錆性に優れる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="38" customHeight="1">
+      <c r="B40" s="23" t="n">
+        <v>36</v>
+      </c>
+      <c r="C40" s="23" t="inlineStr">
+        <is>
+          <t>製品</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>アニオン電着塗料</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F40" s="21" t="inlineStr">
+        <is>
+          <t>Anionic E-coat</t>
+        </is>
+      </c>
+      <c r="G40" s="13" t="inlineStr">
+        <is>
+          <t>酸中和ポリエステル/アクリル樹脂を使用。電子部品等。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="38" customHeight="1">
+      <c r="B41" s="23" t="n">
+        <v>37</v>
+      </c>
+      <c r="C41" s="23" t="inlineStr">
+        <is>
+          <t>製品</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>UV 硬化塗料</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F41" s="21" t="inlineStr">
+        <is>
+          <t>UV-curable Coating</t>
+        </is>
+      </c>
+      <c r="G41" s="13" t="inlineStr">
+        <is>
+          <t>光開始剤を含有し、紫外線照射で瞬時に硬化する塗料。木工・印刷・プラ向け。遮光保管が必要。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="38" customHeight="1">
+      <c r="B42" s="23" t="n">
+        <v>38</v>
+      </c>
+      <c r="C42" s="23" t="inlineStr">
+        <is>
+          <t>製品</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>ハイソリッド塗料</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F42" s="21" t="inlineStr">
+        <is>
+          <t>High-Solid Paint</t>
+        </is>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>固形分比率を高め、溶剤を減らした低 VOC 塗料。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="38" customHeight="1">
+      <c r="B43" s="23" t="n">
+        <v>39</v>
+      </c>
+      <c r="C43" s="23" t="inlineStr">
+        <is>
+          <t>製品</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>2 液型塗料</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>に-えきがた-</t>
+        </is>
+      </c>
+      <c r="F43" s="21" t="inlineStr">
+        <is>
+          <t>Two-component (2K)</t>
+        </is>
+      </c>
+      <c r="G43" s="13" t="inlineStr">
+        <is>
+          <t>主剤と硬化剤を使用直前に混合する塗料。ポットライフ管理が必要。自動車補修・防食で多用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="38" customHeight="1">
+      <c r="B44" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="C44" s="19" t="inlineStr">
+        <is>
+          <t>品質</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>ΔE / 色差</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>デルタイー</t>
+        </is>
+      </c>
+      <c r="F44" s="21" t="inlineStr">
+        <is>
+          <t>Color Difference</t>
+        </is>
+      </c>
+      <c r="G44" s="13" t="inlineStr">
+        <is>
+          <t>標準色と試料色の差を CIE L*a*b* 空間で表現した指標。塗料調色では ΔE &lt; 0.8〜1.5 が合格目安。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="38" customHeight="1">
+      <c r="B45" s="19" t="n">
+        <v>41</v>
+      </c>
+      <c r="C45" s="19" t="inlineStr">
+        <is>
+          <t>品質</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>隠蔽率</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>いんぺいりつ</t>
+        </is>
+      </c>
+      <c r="F45" s="21" t="inlineStr">
+        <is>
+          <t>Hiding Power</t>
+        </is>
+      </c>
+      <c r="G45" s="13" t="inlineStr">
+        <is>
+          <t>塗膜が下地を覆い隠す能力。白黒模様紙上に塗装して測定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="38" customHeight="1">
+      <c r="B46" s="19" t="n">
+        <v>42</v>
+      </c>
+      <c r="C46" s="19" t="inlineStr">
+        <is>
+          <t>品質</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>粘度</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>ねんど</t>
+        </is>
+      </c>
+      <c r="F46" s="21" t="inlineStr">
+        <is>
+          <t>Viscosity</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t>流動性の指標。フォードカップ・ストーマー粘度計・B 型粘度計で測定。塗料の作業性に直結。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="38" customHeight="1">
+      <c r="B47" s="19" t="n">
+        <v>43</v>
+      </c>
+      <c r="C47" s="19" t="inlineStr">
+        <is>
+          <t>品質</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>フォードカップ</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F47" s="21" t="inlineStr">
+        <is>
+          <t>Ford Cup</t>
+        </is>
+      </c>
+      <c r="G47" s="13" t="inlineStr">
+        <is>
+          <t>規定容量のカップから塗料が流出する時間で粘度を測定する簡易計器。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="38" customHeight="1">
+      <c r="B48" s="19" t="n">
+        <v>44</v>
+      </c>
+      <c r="C48" s="19" t="inlineStr">
+        <is>
+          <t>品質</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>固形分</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>こけいぶん</t>
+        </is>
+      </c>
+      <c r="F48" s="21" t="inlineStr">
+        <is>
+          <t>Solid Content / NV</t>
+        </is>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>塗料中の不揮発成分の重量比率。塗膜形成に直接寄与する成分量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="38" customHeight="1">
+      <c r="B49" s="19" t="n">
+        <v>45</v>
+      </c>
+      <c r="C49" s="19" t="inlineStr">
+        <is>
+          <t>品質</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>ドライダウン現象</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" s="21" t="inlineStr">
+        <is>
+          <t>Dry-down Effect</t>
+        </is>
+      </c>
+      <c r="G49" s="13" t="inlineStr">
+        <is>
+          <t>水性塗料で乾燥前後で色味が変わる現象。調色時に乾燥色 (Dry) を参照する必要がある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="38" customHeight="1">
+      <c r="B50" s="19" t="n">
+        <v>46</v>
+      </c>
+      <c r="C50" s="19" t="inlineStr">
+        <is>
+          <t>品質</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>ゲル化時間</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" s="21" t="inlineStr">
+        <is>
+          <t>Gel Time</t>
+        </is>
+      </c>
+      <c r="G50" s="13" t="inlineStr">
+        <is>
+          <t>粉体塗料を加熱して流動性を失うまでの時間。硬化反応の活性度の指標。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="38" customHeight="1">
+      <c r="B51" s="19" t="n">
+        <v>47</v>
+      </c>
+      <c r="C51" s="19" t="inlineStr">
+        <is>
+          <t>品質</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>MEQ</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F51" s="21" t="inlineStr">
+        <is>
+          <t>Milli-equivalents</t>
+        </is>
+      </c>
+      <c r="G51" s="13" t="inlineStr">
+        <is>
+          <t>電着塗料の中和度を示す。樹脂 100 g 当たりの中和剤当量。塗料管理の重要指標。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="38" customHeight="1">
+      <c r="B52" s="19" t="n">
+        <v>48</v>
+      </c>
+      <c r="C52" s="19" t="inlineStr">
+        <is>
+          <t>品質</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>塗着効率</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>とちゃくこうりつ</t>
+        </is>
+      </c>
+      <c r="F52" s="21" t="inlineStr">
+        <is>
+          <t>Transfer Efficiency</t>
+        </is>
+      </c>
+      <c r="G52" s="13" t="inlineStr">
+        <is>
+          <t>吹付塗料のうち被塗物に付着した割合。粉体塗料は回収再利用で理論ほぼ 100% に到達可能。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="38" customHeight="1">
+      <c r="B53" s="24" t="n">
+        <v>49</v>
+      </c>
+      <c r="C53" s="24" t="inlineStr">
+        <is>
+          <t>物流・容器</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>一斗缶</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>いっとかん</t>
+        </is>
+      </c>
+      <c r="F53" s="21" t="inlineStr">
+        <is>
+          <t>18L Can</t>
+        </is>
+      </c>
+      <c r="G53" s="13" t="inlineStr">
+        <is>
+          <t>塗料・油類の代表的な容器。容量 18 L、別名「石油缶」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="38" customHeight="1">
+      <c r="B54" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="C54" s="24" t="inlineStr">
+        <is>
+          <t>物流・容器</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>IBC コンテナ</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F54" s="21" t="inlineStr">
+        <is>
+          <t>Intermediate Bulk Container</t>
+        </is>
+      </c>
+      <c r="G54" s="13" t="inlineStr">
+        <is>
+          <t>1,000 L 級の樹脂タンク。中間バルク容器とも。直販ルートで自動車 OEM 等に供給。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="38" customHeight="1">
+      <c r="B55" s="24" t="n">
+        <v>51</v>
+      </c>
+      <c r="C55" s="24" t="inlineStr">
+        <is>
+          <t>物流・容器</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>フレコン</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" s="21" t="inlineStr">
+        <is>
+          <t>Flexible Container / FIBC</t>
+        </is>
+      </c>
+      <c r="G55" s="13" t="inlineStr">
+        <is>
+          <t>500〜1,000 kg の柔軟容器。粉体塗料・体質顔料の輸送に多用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="38" customHeight="1">
+      <c r="B56" s="24" t="n">
+        <v>52</v>
+      </c>
+      <c r="C56" s="24" t="inlineStr">
+        <is>
+          <t>物流・容器</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>タンクローリー</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" s="21" t="inlineStr">
+        <is>
+          <t>Tank Truck</t>
+        </is>
+      </c>
+      <c r="G56" s="13" t="inlineStr">
+        <is>
+          <t>液体一括輸送車両。電着塗料や OEM 直販で使用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="38" customHeight="1">
+      <c r="B57" s="24" t="n">
+        <v>53</v>
+      </c>
+      <c r="C57" s="24" t="inlineStr">
+        <is>
+          <t>物流・容器</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>VMI</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>ヴイエムアイ</t>
+        </is>
+      </c>
+      <c r="F57" s="21" t="inlineStr">
+        <is>
+          <t>Vendor Managed Inventory</t>
+        </is>
+      </c>
+      <c r="G57" s="13" t="inlineStr">
+        <is>
+          <t>サプライヤーが顧客の在庫を管理する方式。自動車 OEM 向け塗料で標準的。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="38" customHeight="1">
+      <c r="B58" s="24" t="n">
+        <v>54</v>
+      </c>
+      <c r="C58" s="24" t="inlineStr">
+        <is>
+          <t>物流・容器</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>JIT</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>ジット</t>
+        </is>
+      </c>
+      <c r="F58" s="21" t="inlineStr">
+        <is>
+          <t>Just-In-Time</t>
+        </is>
+      </c>
+      <c r="G58" s="13" t="inlineStr">
+        <is>
+          <t>必要な時に必要な量を納入する方式。自動車塗装ラインで欠品ゼロが至上命題。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="38" customHeight="1">
+      <c r="B59" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="C59" s="25" t="inlineStr">
+        <is>
+          <t>規制・安全</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>消防法</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>しょうぼうほう</t>
+        </is>
+      </c>
+      <c r="F59" s="21" t="inlineStr">
+        <is>
+          <t>Fire Service Act (Japan)</t>
+        </is>
+      </c>
+      <c r="G59" s="13" t="inlineStr">
+        <is>
+          <t>塗料の主原料・製品 (引火性液体) を規制する日本の法律。第 4 類に分類。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="38" customHeight="1">
+      <c r="B60" s="25" t="n">
+        <v>56</v>
+      </c>
+      <c r="C60" s="25" t="inlineStr">
+        <is>
+          <t>規制・安全</t>
+        </is>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>危険物第 4 類</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F60" s="21" t="inlineStr">
+        <is>
+          <t>Class 4 Hazardous Materials</t>
+        </is>
+      </c>
+      <c r="G60" s="13" t="inlineStr">
+        <is>
+          <t>引火性液体。第 1 石油類 (引火点 21℃未満)・第 2 石油類 (21〜70℃)・第 3 石油類 (70〜200℃) 等に細分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="38" customHeight="1">
+      <c r="B61" s="25" t="n">
+        <v>57</v>
+      </c>
+      <c r="C61" s="25" t="inlineStr">
+        <is>
+          <t>規制・安全</t>
+        </is>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>指定数量</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>していすうりょう</t>
+        </is>
+      </c>
+      <c r="F61" s="21" t="inlineStr">
+        <is>
+          <t>Designated Quantity</t>
+        </is>
+      </c>
+      <c r="G61" s="13" t="inlineStr">
+        <is>
+          <t>消防法で危険物の保管・取扱いに規制をかける基準量。倍数管理で倉庫構造が決まる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="38" customHeight="1">
+      <c r="B62" s="25" t="n">
+        <v>58</v>
+      </c>
+      <c r="C62" s="25" t="inlineStr">
+        <is>
+          <t>規制・安全</t>
+        </is>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>VOC</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>ブイオーシー</t>
+        </is>
+      </c>
+      <c r="F62" s="21" t="inlineStr">
+        <is>
+          <t>Volatile Organic Compounds</t>
+        </is>
+      </c>
+      <c r="G62" s="13" t="inlineStr">
+        <is>
+          <t>揮発性有機化合物。光化学スモッグの原因。大気汚染防止法で規制。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="38" customHeight="1">
+      <c r="B63" s="25" t="n">
+        <v>59</v>
+      </c>
+      <c r="C63" s="25" t="inlineStr">
+        <is>
+          <t>規制・安全</t>
+        </is>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>PRTR</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>ピーアールティーアール</t>
+        </is>
+      </c>
+      <c r="F63" s="21" t="inlineStr">
+        <is>
+          <t>Pollutant Release and Transfer Register</t>
+        </is>
+      </c>
+      <c r="G63" s="13" t="inlineStr">
+        <is>
+          <t>化学物質排出移動量届出制度 (経産省・環境省)。塗料関連物質も対象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="38" customHeight="1">
+      <c r="B64" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="C64" s="25" t="inlineStr">
+        <is>
+          <t>規制・安全</t>
+        </is>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>GHS</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>ジーエイチエス</t>
+        </is>
+      </c>
+      <c r="F64" s="21" t="inlineStr">
+        <is>
+          <t>Globally Harmonized System</t>
+        </is>
+      </c>
+      <c r="G64" s="13" t="inlineStr">
+        <is>
+          <t>化学品の分類・表示の世界共通システム。塗料缶にも GHS ピクトグラム表示が必要。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="38" customHeight="1">
+      <c r="B65" s="25" t="n">
+        <v>61</v>
+      </c>
+      <c r="C65" s="25" t="inlineStr">
+        <is>
+          <t>規制・安全</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>REACH</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>リーチ</t>
+        </is>
+      </c>
+      <c r="F65" s="21" t="inlineStr">
+        <is>
+          <t>Registration, Evaluation, Authorisation of Chemicals</t>
+        </is>
+      </c>
+      <c r="G65" s="13" t="inlineStr">
+        <is>
+          <t>EU の化学品規制。塗料原料も登録対象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="38" customHeight="1">
+      <c r="B66" s="25" t="n">
+        <v>62</v>
+      </c>
+      <c r="C66" s="25" t="inlineStr">
+        <is>
+          <t>規制・安全</t>
+        </is>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>RoHS</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>ローズ</t>
+        </is>
+      </c>
+      <c r="F66" s="21" t="inlineStr">
+        <is>
+          <t>Restriction of Hazardous Substances</t>
+        </is>
+      </c>
+      <c r="G66" s="13" t="inlineStr">
+        <is>
+          <t>EU の有害物質使用制限指令。鉛・カドミウム等を制限。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="38" customHeight="1">
+      <c r="B67" s="25" t="n">
+        <v>63</v>
+      </c>
+      <c r="C67" s="25" t="inlineStr">
+        <is>
+          <t>規制・安全</t>
+        </is>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>産業廃棄物</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F67" s="21" t="inlineStr">
+        <is>
+          <t>Industrial Waste</t>
+        </is>
+      </c>
+      <c r="G67" s="13" t="inlineStr">
+        <is>
+          <t>事業活動で発生する廃棄物。塗料関連は燃え殻・廃酸・廃アルカリ・廃油・廃プラ等に区分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="38" customHeight="1">
+      <c r="B68" s="25" t="n">
+        <v>64</v>
+      </c>
+      <c r="C68" s="25" t="inlineStr">
+        <is>
+          <t>規制・安全</t>
+        </is>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>特別管理産業廃棄物</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>とくべつかんり-</t>
+        </is>
+      </c>
+      <c r="F68" s="21" t="inlineStr">
+        <is>
+          <t>Specially Controlled Industrial Waste</t>
+        </is>
+      </c>
+      <c r="G68" s="13" t="inlineStr">
+        <is>
+          <t>爆発性・毒性・感染性等のある特に管理が必要な産廃。引火点 70℃未満の廃油 (廃シンナー) が該当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="38" customHeight="1">
+      <c r="B69" s="26" t="n">
+        <v>65</v>
+      </c>
+      <c r="C69" s="26" t="inlineStr">
+        <is>
+          <t>環境・省エネ</t>
+        </is>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>RTO</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>アールティーオー</t>
+        </is>
+      </c>
+      <c r="F69" s="21" t="inlineStr">
+        <is>
+          <t>Regenerative Thermal Oxidizer</t>
+        </is>
+      </c>
+      <c r="G69" s="13" t="inlineStr">
+        <is>
+          <t>蓄熱燃焼式 VOC 処理装置。排ガスを 700〜800℃で燃焼し VOC を CO₂・水に分解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="38" customHeight="1">
+      <c r="B70" s="26" t="n">
+        <v>66</v>
+      </c>
+      <c r="C70" s="26" t="inlineStr">
+        <is>
+          <t>環境・省エネ</t>
+        </is>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>活性炭吸着</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>かっせいたんきゅうちゃく</t>
+        </is>
+      </c>
+      <c r="F70" s="21" t="inlineStr">
+        <is>
+          <t>Activated Carbon Adsorption</t>
+        </is>
+      </c>
+      <c r="G70" s="13" t="inlineStr">
+        <is>
+          <t>活性炭で VOC を吸着除去する方法。低濃度に有効。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="38" customHeight="1">
+      <c r="B71" s="26" t="n">
+        <v>67</v>
+      </c>
+      <c r="C71" s="26" t="inlineStr">
+        <is>
+          <t>環境・省エネ</t>
+        </is>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>Scope 1/2/3</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F71" s="21" t="inlineStr">
+        <is>
+          <t>GHG Protocol Scopes</t>
+        </is>
+      </c>
+      <c r="G71" s="13" t="inlineStr">
+        <is>
+          <t>Scope 1=自社直接排出、Scope 2=購入電力等、Scope 3=サプライチェーン上下流。塗料業は Scope 3 が圧倒的に大きい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="38" customHeight="1">
+      <c r="B72" s="26" t="n">
+        <v>68</v>
+      </c>
+      <c r="C72" s="26" t="inlineStr">
+        <is>
+          <t>環境・省エネ</t>
+        </is>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>UF (限外ろ過)</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F72" s="21" t="inlineStr">
+        <is>
+          <t>Ultrafiltration</t>
+        </is>
+      </c>
+      <c r="G72" s="13" t="inlineStr">
+        <is>
+          <t>膜分離技術。電着塗装ラインで回収洗浄水中の塗料分を濃縮・再利用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="38" customHeight="1">
+      <c r="B73" s="26" t="n">
+        <v>69</v>
+      </c>
+      <c r="C73" s="26" t="inlineStr">
+        <is>
+          <t>環境・省エネ</t>
+        </is>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>ピギング</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F73" s="21" t="inlineStr">
+        <is>
+          <t>Pigging</t>
+        </is>
+      </c>
+      <c r="G73" s="13" t="inlineStr">
+        <is>
+          <t>配管内に円筒状のピグを通して残液を回収する技術。塗料の配管残ロス削減に有効。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="38" customHeight="1">
+      <c r="B74" s="26" t="n">
+        <v>70</v>
+      </c>
+      <c r="C74" s="26" t="inlineStr">
+        <is>
+          <t>環境・省エネ</t>
+        </is>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>蒸留再生</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>じょうりゅうさいせい</t>
+        </is>
+      </c>
+      <c r="F74" s="21" t="inlineStr">
+        <is>
+          <t>Solvent Distillation / Recovery</t>
+        </is>
+      </c>
+      <c r="G74" s="13" t="inlineStr">
+        <is>
+          <t>廃シンナーを蒸留して再生溶剤として回収する技術。社内設置で処理コストを 1/3 程度に削減可能。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B2:D2"/>
+  <mergeCells count="1">
+    <mergeCell ref="B2:F2"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId25"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>